--- a/vehicle_list_8801681373638.xlsx
+++ b/vehicle_list_8801681373638.xlsx
@@ -418,7 +418,7 @@
         <v>Test-1</v>
       </c>
       <c r="B2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>2</v>
